--- a/docs/blazeup/Bug_Tracker.xlsx
+++ b/docs/blazeup/Bug_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Tracker'!$A$1:$Q$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Tracker'!$A$1:$P$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -71,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -79,6 +79,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -529,25 +533,20 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>BE Ticket</t>
+          <t>Reported By</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Reported By</t>
+          <t>Date Opened</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Date Opened</t>
+          <t>Date Closed</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Date Closed</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -559,7 +558,7 @@
           <t>BUG-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="3" t="n">
         <v>2060122</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -612,19 +611,18 @@
           <t>AssertionError: re-granting must not duplicate active cert</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>be_gap — missing idempotency guard</t>
         </is>
@@ -636,7 +634,7 @@
           <t>BUG-002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="3" t="n">
         <v>2060208</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -689,19 +687,18 @@
           <t>AssertionError: approved deal must stamp rate + rate table version</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>be_gap</t>
         </is>
@@ -713,7 +710,7 @@
           <t>BUG-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="3" t="n">
         <v>2060221</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -766,19 +763,18 @@
           <t>CHECK ghost planId (verified absent) -&gt; FAIL (status=201)</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>be_gap — no FK validation</t>
         </is>
@@ -790,9 +786,24 @@
           <t>BUG-004</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="4" t="n">
         <v>2060713</v>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PARTNER_API_PARTNER_USERS_013</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Partner Users</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>Major</t>
@@ -810,28 +821,1167 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FAIL | [2/2] The partner must NOT end up with a duplicate-email user (247ms) -- AssertionError: re-inviting must not duplicate: expected 1 user for qa.auto+gtaylor@mailinator.com, got 2 — BE creates a</t>
+          <t>Inviting a duplicate email creates a second user</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Reject (409) or idempotent — no duplicate user</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Returns 201; two users share one login</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AssertionError: re-inviting must not duplicate user</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>QA</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>auto-added by AI triage</t>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>be_gap — no duplicate-email guard</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BUG-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>2061003</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PARTNER_API_AUTH_ACCESS_CONTROL_003</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AUTH_ACCESS_CONTROL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>cross-partner access - a partner cannot read another's deal.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>404 (preferred, hides existence) or 403 for cross-partner access</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Returns 400 (mislabels a valid request as malformed); isolation holds (no data leak)</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>FAIL | [1/1] Partner B requests partner A's deal → refused, no leak (333ms) -- AssertionError: cross-partner access should be 404 (preferred) or 403, got 400 — BE returns 400 (a valid request, not a bad one); confirm with BE</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>AI Triage</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>be_gap — wrong status code for authz; confirm with BE (should be 404)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BUG-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>2060231</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PARTNER_API_DEAL_REGISTRATION_PIPELINE_031</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DEAL_REGISTRATION_PIPELINE</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>GET deal by a well-formed but non-existent id returns 400 instead of 404</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>404 Not Found for a well-formed but non-existent deal id</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>400 Bad Request with message "Deal 000000000000000000000000 not found" (status contradicts message)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>test_partner_api_deal_registration_pipeline_031 [1/2]: expected 404, got 400, msg="Deal 000000000000000000000000 not found"</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>QA (review)</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>REST-hygiene: malformed id -&gt; 400 is correct; a well-formed absent id should be 404. be_gap, excluded from merge gate. Confirm with BE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BUG-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>2060232</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PARTNER_API_DEAL_REGISTRATION_PIPELINE_032</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>DEAL_REGISTRATION_PIPELINE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>lose deal on a well-formed but non-existent id returns 400 instead of 404</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>404 Not Found for a well-formed but non-existent deal id</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>400 Bad Request with message "Deal 000000000000000000000000 not found" (status contradicts message)</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>test_partner_api_deal_registration_pipeline_032 [2/3]: expected 404, got 400, msg="Deal 000000000000000000000000 not found"</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>QA (review)</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Same root cause as BUG-006 (get-by-id). Ghost id -&gt; should be 404. Illegal-transition (400) and malformed (400) cases are correct. be_gap, excluded from merge gate. Confirm with BE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BUG-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>2060228</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PARTNER_API_DEAL_REGISTRATION_PIPELINE_028</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>DEAL_REGISTRATION_PIPELINE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>approve deal on a well-formed but non-existent id returns 400 instead of 404</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>404 Not Found for a well-formed but non-existent deal id</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>400 Bad Request with message "Deal 000000000000000000000000 not found" (status contradicts message)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>test_partner_api_deal_registration_pipeline_028 [1/3]: expected 404, got 400, msg="Deal 000000000000000000000000 not found"</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>QA (review)</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Same root cause as BUG-006/007 (ghost id -&gt; should be 404). Malformed (400) and illegal-transition (400) cases are correct. be_gap, excluded from merge gate. Confirm with BE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BUG-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>2060229</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PARTNER_API_DEAL_REGISTRATION_PIPELINE_029</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>DEAL_REGISTRATION_PIPELINE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>resolve-conflict on a well-formed but non-existent id returns 400 instead of 404</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>404 Not Found for a well-formed but non-existent deal id</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>400 Bad Request with message "Deal 000000000000000000000000 not found" (status contradicts message)</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>test_partner_api_deal_registration_pipeline_029 [6/6]: expected 404, got 400, msg="Deal 000000000000000000000000 not found"</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>QA (review)</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Same root cause as BUG-006/007/008 (ghost id -&gt; should be 404). Validation/format/state cases (400) are correct. be_gap, excluded from merge gate. Confirm with BE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BUG-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>2060230</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PARTNER_API_DEAL_REGISTRATION_PIPELINE_030</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>DEAL_REGISTRATION_PIPELINE</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>extend-protection on a well-formed but non-existent id returns 400 instead of 404</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>404 Not Found for a well-formed but non-existent deal id</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>400 Bad Request with message "Deal 000000000000000000000000 not found" (status contradicts message)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>test_partner_api_deal_registration_pipeline_030 [8/8]: expected 404, got 400, msg="Deal 000000000000000000000000 not found"</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>QA (review)</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Same root cause as BUG-006/007/008/009 (ghost id -&gt; should be 404). Body-validation/boundary/format/malformed cases (400) are correct. be_gap, excluded from merge gate. Confirm with BE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BUG-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>2061111</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PARTNER_API_DEAL_APPROVAL_QUEUE_011</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>DEAL_APPROVAL_QUEUE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>reject deal on a well-formed but non-existent id returns 400 instead of 404</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>404 Not Found for a well-formed but non-existent deal id</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>400 Bad Request with message "Deal 000000000000000000000000 not found" (status contradicts message)</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>test_partner_api_deal_approval_queue_011 [1/3]: expected 404, got 400, msg="Deal 000000000000000000000000 not found"</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>QA (review)</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Same root cause as BUG-006..010 (ghost path id -&gt; should be 404). Malformed (400) and illegal-transition (400) cases are correct. be_gap, excluded from merge gate. Confirm with BE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BUG-012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>2060113</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PARTNER_API_PARTNER_ACCOUNT_MANAGEMENT_013</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PARTNER_ACCOUNT_MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>approve partner: well-formed but non-existent partner id returns 400 instead of 404</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>404 Not Found for a well-formed but non-existent partner id</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>400 Bad Request with message "Partner 000000000000000000000000 not found" (status contradicts message)</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>test_partner_api_partner_account_management_013 [1/3]: expected 404, got 400, msg="Partner 000000000000000000000000 not found"</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>QA (review)</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Same root cause as BUG-006..011 (ghost path id -&gt; should be 404), now on partner-id endpoints. Other cases (validation/format/transition, all 400) are correct. be_gap, excluded from merge gate. Confirm with BE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BUG-013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>2060114</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PARTNER_API_PARTNER_ACCOUNT_MANAGEMENT_014</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PARTNER_ACCOUNT_MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>deactivate partner: well-formed but non-existent partner id returns 400 instead of 404</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>404 Not Found for a well-formed but non-existent partner id</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>400 Bad Request with message "Partner 000000000000000000000000 not found" (status contradicts message)</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>test_partner_api_partner_account_management_014 [1/3]: expected 404, got 400, msg="Partner 000000000000000000000000 not found"</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>QA (review)</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Same root cause as BUG-006..011 (ghost path id -&gt; should be 404), now on partner-id endpoints. Other cases (validation/format/transition, all 400) are correct. be_gap, excluded from merge gate. Confirm with BE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BUG-014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>2060115</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PARTNER_API_PARTNER_ACCOUNT_MANAGEMENT_015</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PARTNER_ACCOUNT_MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>change-tier partner: well-formed but non-existent partner id returns 400 instead of 404</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>404 Not Found for a well-formed but non-existent partner id</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>400 Bad Request with message "Partner 000000000000000000000000 not found" (status contradicts message)</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>test_partner_api_partner_account_management_015 [6/6]: expected 404, got 400, msg="Partner 000000000000000000000000 not found"</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>QA (review)</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Same root cause as BUG-006..011 (ghost path id -&gt; should be 404), now on partner-id endpoints. Other cases (validation/format/transition, all 400) are correct. be_gap, excluded from merge gate. Confirm with BE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BUG-015</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>2060120</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PARTNER_API_PARTNER_ACCOUNT_MANAGEMENT_020</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PARTNER_ACCOUNT_MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>grant-certification on a well-formed but non-existent userId returns 400 instead of 404</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>404 Not Found for a well-formed but non-existent userId</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>400 Bad Request with message "User 000000000000000000000000 not found" (status contradicts message)</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>test_partner_api_partner_account_management_020 [4/4]: expected 404, got 400, msg="User 000000000000000000000000 not found"</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>QA (review)</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Same root cause as BUG-006..014 (ghost path id -&gt; should be 404), on partner-users/{userId} endpoint. Validation/format cases (400) are correct. be_gap, excluded from merge gate. Confirm with BE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BUG-016</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>2060714</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PARTNER_API_PARTNER_USERS_014</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PARTNER_USERS</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>reset-password on a well-formed but non-existent userId returns 400 instead of 404</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>404 Not Found for a well-formed but non-existent userId</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>400 Bad Request with message "User 000000000000000000000000 not found" (status contradicts message)</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>test_partner_api_partner_users_014 [1/2]: expected 404, got 400, msg="User 000000000000000000000000 not found"</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>QA (review)</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Same root cause as BUG-006..015 (ghost path id -&gt; should be 404), on partner-users/{userId}/reset-password. Malformed (400) is correct. be_gap, excluded from merge gate. Confirm with BE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BUG-017</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>2060414</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PARTNER_API_TERRITORIES_014</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>TERRITORIES</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>get-territory-by-id on a well-formed but non-existent id returns 400 instead of 404</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>404 Not Found for a well-formed but non-existent / already-removed territory id</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>400 Bad Request with message "Territory ... not found" (status contradicts message)</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>test_partner_api_territories_014 [1/2]: expected 404, got 400, msg="Territory 000000000000000000000000 not found"</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>QA (review)</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Same root cause as BUG-006..016 (ghost path id -&gt; should be 404), on territories endpoints. Malformed (400) is correct. be_gap, excluded from merge gate. Confirm with BE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BUG-018</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>2060415</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PARTNER_API_TERRITORIES_015</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>TERRITORIES</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>delete territory on a non-existent / already-removed id returns 400 instead of 404</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>404 Not Found for a well-formed but non-existent / already-removed territory id</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>400 Bad Request with message "Territory ... not found" (status contradicts message)</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>test_partner_api_territories_015 [1/3] + [3/3]: expected 404, got 400 (ghost id AND already-removed), msg="Territory ... not found"</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>QA (review)</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Same root cause as BUG-006..016 (ghost path id -&gt; should be 404), on territories endpoints. Malformed (400) is correct. be_gap, excluded from merge gate. Confirm with BE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BUG-019</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>2060512</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PARTNER_API_CERTIFICATIONS_SA_012</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>CERTIFICATIONS_SA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>revoke-certification not-found targets (ghost user / cert-not-held / already-revoked) return 400 instead of 404</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>404 Not Found when the revoke target (user or active cert) does not exist</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>400 Bad Request with a "not found" message (User ... not found / Active ... certification not found)</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>test_partner_api_certifications_sa_012: cases 2,3,5 expected 404, got 400 (msg contains not found)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>QA (review)</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Same root cause as BUG-006..018 (not-found -&gt; should be 404). Missing-reason (400) and malformed-id (400) are correct. be_gap, excluded from merge gate. Confirm with BE.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/blazeup/Bug_Tracker.xlsx
+++ b/docs/blazeup/Bug_Tracker.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1980,6 +1980,83 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BUG-020</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>2060234</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PARTNER_API_DEAL_REGISTRATION_PIPELINE_034</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>DEAL_REGISTRATION_PIPELINE</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Win deal: WinDealDto required fields not enforced (companyWebsite/industry/adminFirstName/adminLastName)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>400 when a required win-intake field is missing (per WinDealDto required list)</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>201 - deal is won even with all required fields missing (empty body also wins)</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>test_partner_api_deal_registration_pipeline_034 [1-4/8]: missing companyWebsite/industry/adminFirstName/adminLastName each returned 201 (expected 400)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>QA (review)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>WinDealDto (POST /v1/sa/deals/{id}/win) declares these 4 fields required in OpenAPI but the controller does not enforce them. Tenant-provisioning intake can be won with no company/admin data. be_gap, excluded from merge gate. Confirm with BE.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/blazeup/Bug_Tracker.xlsx
+++ b/docs/blazeup/Bug_Tracker.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Bug Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Tracker'!$A$1:$P$1</definedName>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2057,6 +2057,71 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BUG-021</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>12060101</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PARTNER_UI_PARTNER_PORTAL_SHELL_001</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PARTNER_PORTAL_SHELL</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>every primary nav page loads via URL (no MFE error).</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Page [apps] FAILED - Partner Portal section 'apps' rendered its shell but the CONTENT failed to load: banner 'Failed to load' is visible in &lt;main&gt;. Data-fetch/backend issue for this page — confirm with BE.</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>AI Triage</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>auto-added by AI triage</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/blazeup/Bug_Tracker.xlsx
+++ b/docs/blazeup/Bug_Tracker.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.14785714285714" bestFit="1" customWidth="1" style="11" min="1" max="1"/>
@@ -2079,125 +2079,129 @@
       <c r="P22" s="7" t="n"/>
     </row>
     <row r="23" ht="58.5" customHeight="1">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="7" t="n"/>
-      <c r="J23" s="7" t="n"/>
-      <c r="K23" s="7" t="n"/>
-      <c r="L23" s="7" t="n"/>
-      <c r="M23" s="7" t="n"/>
-      <c r="N23" s="7" t="n"/>
-      <c r="O23" s="7" t="n"/>
-      <c r="P23" s="7" t="n"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BUG-API-021</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>(no TC yet — DELETE partner is never asserted)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PARTNER_ACCOUNT_MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>DELETE /v1/sa/partners/{id} reports success but only soft-deletes: the record stays in GET /v1/sa/partners with status='suspended', so 'deleted' and 'suspended' are indistinguishable and no client can clean up data it created.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>DELETE removes the partner. Or, if soft delete is intentional: deleted records are excluded from GET /v1/sa/partners by default (or expose a deleted/deletedAt flag) so a caller can tell a deleted partner from a suspended one.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>HTTP 200 {"statusCode":200,"message":"Partner deleted successfully"} — but the record is still returned by GET /v1/sa/partners with status='suspended' and internalNotes='Deleted by SA'. On stgsa 2026-08-06 all 1821 partner records are QA-AUTO test leftovers, the bulk of them already 'deleted' this way.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Probe on stgsa 2026-08-06: create partner -&gt; DELETE (200) -&gt; GET /v1/sa/partners?search=&lt;name&gt; still returns it at +0s/+3s/+10s with status='suspended', internalNotes='Deleted by SA'. Reproduced from a UI run: 'CLEANUP LEAK: DELETE partner ... returned HTTP 200 but the record is STILL listed'.</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>QA (review)</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Impact on automation: every created_resources cleanup receives 200 and reports success while removing nothing, so shared staging grows unbounded (~1.8k QA-AUTO partners) and cross-partner conflict tests get noisier over time. No TC asserts that DELETE removes the record (delete_partner is only a cleanup callback) — recommend adding one. Also missing entirely: a DELETE for deals, and a delete/revoke for partner-users (only certifications have one), so data created by PARTNER_UI_MY_PIPELINE_005 and PARTNER_UI_PARTNER_TEAM_001 cannot be cleaned at all. utils/cleanup_staging.py + utils/ui_cleanup.py now verify the effect instead of trusting the 200.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="18.75" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="7" t="n"/>
+      <c r="I24" s="7" t="n"/>
+      <c r="J24" s="7" t="n"/>
+      <c r="K24" s="7" t="n"/>
+      <c r="L24" s="7" t="n"/>
+      <c r="M24" s="7" t="n"/>
+      <c r="N24" s="7" t="n"/>
+      <c r="O24" s="7" t="n"/>
+      <c r="P24" s="7" t="n"/>
+    </row>
+    <row r="25" ht="18.75" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
-      <c r="I24" s="6" t="n"/>
-      <c r="J24" s="6" t="n"/>
-      <c r="K24" s="6" t="n"/>
-      <c r="L24" s="6" t="n"/>
-      <c r="M24" s="6" t="n"/>
-      <c r="N24" s="6" t="n"/>
-      <c r="O24" s="6" t="n"/>
-      <c r="P24" s="6" t="n"/>
-    </row>
-    <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>BUG-UI-001</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="n">
-        <v>12060101</v>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>PARTNER_UI_PARTNER_PORTAL_SHELL_001</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Partner</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>PARTNER_PORTAL_SHELL</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>every primary nav page loads via URL (no MFE error).</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>every primary nav page loads via URL (no MFE error).</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="n"/>
-      <c r="L25" s="7" t="inlineStr">
-        <is>
-          <t>Page [apps] FAILED - Partner Portal section 'apps' rendered its shell but the CONTENT failed to load: banner 'Failed to load' is visible in &lt;main&gt;. Data-fetch/backend issue for this page — confirm with BE.</t>
-        </is>
-      </c>
-      <c r="M25" s="7" t="inlineStr">
-        <is>
-          <t>AI Triage</t>
-        </is>
-      </c>
-      <c r="N25" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="O25" s="7" t="n"/>
-      <c r="P25" s="7" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="6" t="n"/>
+      <c r="L25" s="6" t="n"/>
+      <c r="M25" s="6" t="n"/>
+      <c r="N25" s="6" t="n"/>
+      <c r="O25" s="6" t="n"/>
+      <c r="P25" s="6" t="n"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>BUG-UI-002</t>
+          <t>BUG-UI-001</t>
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>12060102</v>
+        <v>12060101</v>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>PARTNER_UI_PARTNER_PORTAL_SHELL_002</t>
+          <t>PARTNER_UI_PARTNER_PORTAL_SHELL_001</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -2227,22 +2231,18 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>portal stays usable at mobile width (no h-overflow, nav reachable).</t>
+          <t>every primary nav page loads via URL (no MFE error).</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>portal stays usable at mobile width (no h-overflow, nav reachable).</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>Page [deals] FAILED - 'deals' overflows the mobile viewport by 162px (content does not fit 375px → responsive-layout defect; confirm with FE)</t>
-        </is>
-      </c>
+          <t>every primary nav page loads via URL (no MFE error).</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="n"/>
       <c r="L26" s="7" t="inlineStr">
         <is>
-          <t>Page [deals] FAILED - 'deals' overflows the mobile viewport by 162px (content does not fit 375px → responsive-layout defect; confirm with FE)</t>
+          <t>Page [apps] FAILED - Partner Portal section 'apps' rendered its shell but the CONTENT failed to load: banner 'Failed to load' is visible in &lt;main&gt;. Data-fetch/backend issue for this page — confirm with BE.</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="O26" s="7" t="n"/>
@@ -2261,15 +2261,15 @@
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>BUG-UI-003</t>
+          <t>BUG-UI-002</t>
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>12060203</v>
+        <v>12060102</v>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>PARTNER_UI_MY_PIPELINE_003</t>
+          <t>PARTNER_UI_PARTNER_PORTAL_SHELL_002</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>MY_PIPELINE</t>
+          <t>PARTNER_PORTAL_SHELL</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -2299,22 +2299,22 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>an invalid domain must be rejected with a format error.</t>
+          <t>portal stays usable at mobile width (no h-overflow, nav reachable).</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>an invalid domain must be rejected with a format error.</t>
+          <t>portal stays usable at mobile width (no h-overflow, nav reachable).</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>FAIL | [1/1] Each malformed domain must be rejected (block Next / flag field) (246ms) -- AssertionError: wizard accepts invalid domain(s) ["'@@@' (field kept '@@@', Next enabled, not flagged)", "'ab cd' (field kept 'ab cd', Next enabled, not flagged)</t>
+          <t>Page [deals] FAILED - 'deals' overflows the mobile viewport by 162px (content does not fit 375px → responsive-layout defect; confirm with FE)</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>FAIL | [1/1] Each malformed domain must be rejected (block Next / flag field) (246ms) -- AssertionError: wizard accepts invalid domain(s) ["'@@@' (field kept '@@@', Next enabled, not flagged)", "'ab cd' (field kept 'ab cd', Next enabled, not flagged)", "'notadomain' (field kept 'notadomain', Next en</t>
+          <t>Page [deals] FAILED - 'deals' overflows the mobile viewport by 162px (content does not fit 375px → responsive-layout defect; confirm with FE)</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="O27" s="7" t="n"/>
@@ -2333,165 +2333,161 @@
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
+          <t>BUG-UI-003</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="n">
+        <v>12060203</v>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>PARTNER_UI_MY_PIPELINE_003</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>MY_PIPELINE</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>an invalid domain must be rejected with a format error.</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>an invalid domain must be rejected with a format error.</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>FAIL | [1/1] Each malformed domain must be rejected (block Next / flag field) (246ms) -- AssertionError: wizard accepts invalid domain(s) ["'@@@' (field kept '@@@', Next enabled, not flagged)", "'ab cd' (field kept 'ab cd', Next enabled, not flagged)</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>FAIL | [1/1] Each malformed domain must be rejected (block Next / flag field) (246ms) -- AssertionError: wizard accepts invalid domain(s) ["'@@@' (field kept '@@@', Next enabled, not flagged)", "'ab cd' (field kept 'ab cd', Next enabled, not flagged)", "'notadomain' (field kept 'notadomain', Next en</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>AI Triage</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="O28" s="7" t="n"/>
+      <c r="P28" s="7" t="n"/>
+    </row>
+    <row r="29" ht="18.75" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
           <t>BUG-UI-004</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n">
+      <c r="B29" s="9" t="n">
         <v>12060207</v>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>PARTNER_UI_MY_PIPELINE_007</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Partner</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>MY_PIPELINE</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>CLOSE
 CLOSE
 CLOSE</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>a malformed contact email must be rejected with a format error.</t>
         </is>
       </c>
-      <c r="J28" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>a malformed contact email must be rejected with a format error.</t>
         </is>
       </c>
-      <c r="K28" s="7" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">FAIL | [1/1] Each malformed email must be rejected (block Next / flag field) (246ms) -- AssertionError: wizard accepts malformed email(s) ["'notanemail' (field kept 'notanemail', Next enabled, not flagged)", "'abc@' (field kept 'abc@', Next enabled, </t>
         </is>
       </c>
-      <c r="L28" s="7" t="inlineStr">
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">FAIL | [1/1] Each malformed email must be rejected (block Next / flag field) (246ms) -- AssertionError: wizard accepts malformed email(s) ["'notanemail' (field kept 'notanemail', Next enabled, not flagged)", "'abc@' (field kept 'abc@', Next enabled, not flagged)", "'abc@x' (field kept 'abc@x', Next </t>
         </is>
       </c>
-      <c r="M28" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>AI Triage</t>
         </is>
       </c>
-      <c r="N28" s="7" t="inlineStr">
+      <c r="N29" s="7" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="O28" s="7" t="n"/>
-      <c r="P28" s="7" t="n"/>
-    </row>
-    <row r="29" ht="18.75" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>BUG-UI-005</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="n">
-        <v>12060507</v>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>PARTNER_UI_SA_PARTNER_MODULE_007</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Partner</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>SA_PARTNER_MODULE</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>SA Deal Approval Queue (/partners/deals): deal-list API consistently returns "Server Error - Invalid id: pro-v1" instead of the deals.</t>
-        </is>
-      </c>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>GET deal-list for /partners/deals returns the deals (200); the queue table shows deal rows. No "Invalid id" error.</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="inlineStr">
-        <is>
-          <t>The deal-list fetch consistently returns "Server Error - Invalid id: pro-v1"; the UI shows "No Data Found" and no deal rows load (partners DO have open deals).</t>
-        </is>
-      </c>
-      <c r="L29" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FAIL | [3/3] The Pending Approval + Conflicts queues load without a server error (3161ms) -- AssertionError: the deal approval queues must load their deals, but the deal-list fetch fails with a backend error on: ['Pending Approval: "Server Error Invalid id: \'pro-v1\' Server Error Invalid id: \'"', </t>
-        </is>
-      </c>
-      <c r="M29" s="7" t="inlineStr">
-        <is>
-          <t>AI Triage</t>
-        </is>
-      </c>
-      <c r="N29" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
       <c r="O29" s="7" t="n"/>
-      <c r="P29" s="7" t="inlineStr">
-        <is>
-          <t>Root cause = contract drift: a plan-slug "pro-v1" (string) is used where the API expects a Mongo _id (24-hex), so deal-list id validation fails. CONSISTENT, not intermittent (updated 2026-08-05): earlier "lucky PASS" runs were a TEST race - the assertion ran before the async deal-list error painted; the test now waits for the fetch to settle and fails deterministically. UI test 12060507 renders fine (shell/filters/headers OK); this step reflects the BE defect. Fix BE so deal-list never returns Invalid id: pro-v1.</t>
-        </is>
-      </c>
+      <c r="P29" s="7" t="n"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>BUG-UI-006</t>
+          <t>BUG-UI-005</t>
         </is>
       </c>
       <c r="B30" s="9" t="n">
-        <v>12060511</v>
+        <v>12060507</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>PARTNER_UI_SA_PARTNER_MODULE_011</t>
+          <t>PARTNER_UI_SA_PARTNER_MODULE_007</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -2521,22 +2517,22 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>the SA partner-programme analytics dashboard.</t>
+          <t>SA Deal Approval Queue (/partners/deals): deal-list API consistently returns "Server Error - Invalid id: pro-v1" instead of the deals.</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>the SA partner-programme analytics dashboard.</t>
+          <t>GET deal-list for /partners/deals returns the deals (200); the queue table shows deal rows. No "Invalid id" error.</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>FAIL | [3/3] The analytics data loads without a server error (44ms) -- AssertionError: the analytics dashboard must load its data, but a query fails with a backend error: 'Server Error limit must not be greater than 100 Server Error Invalid p'. The d</t>
+          <t>The deal-list fetch consistently returns "Server Error - Invalid id: pro-v1"; the UI shows "No Data Found" and no deal rows load (partners DO have open deals).</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>FAIL | [3/3] The analytics data loads without a server error (44ms) -- AssertionError: the analytics dashboard must load its data, but a query fails with a backend error: 'Server Error limit must not be greater than 100 Server Error Invalid p'. The dashboard shell renders but a paginated analytics q</t>
+          <t xml:space="preserve">FAIL | [3/3] The Pending Approval + Conflicts queues load without a server error (3161ms) -- AssertionError: the deal approval queues must load their deals, but the deal-list fetch fails with a backend error on: ['Pending Approval: "Server Error Invalid id: \'pro-v1\' Server Error Invalid id: \'"', </t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
@@ -2550,20 +2546,24 @@
         </is>
       </c>
       <c r="O30" s="7" t="n"/>
-      <c r="P30" s="7" t="n"/>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>Root cause = contract drift: a plan-slug "pro-v1" (string) is used where the API expects a Mongo _id (24-hex), so deal-list id validation fails. CONSISTENT, not intermittent (updated 2026-08-05): earlier "lucky PASS" runs were a TEST race - the assertion ran before the async deal-list error painted; the test now waits for the fetch to settle and fails deterministically. UI test 12060507 renders fine (shell/filters/headers OK); this step reflects the BE defect. Fix BE so deal-list never returns Invalid id: pro-v1.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>BUG-UI-007</t>
+          <t>BUG-UI-006</t>
         </is>
       </c>
       <c r="B31" s="9" t="n">
-        <v>12060405</v>
+        <v>12060511</v>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>PARTNER_UI_DASHBOARD_005</t>
+          <t>PARTNER_UI_SA_PARTNER_MODULE_011</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>DASHBOARD</t>
+          <t>SA_PARTNER_MODULE</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -2593,22 +2593,22 @@
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>tier-qualification math (T12M ARR threshold + next-tier delta).</t>
+          <t>the SA partner-programme analytics dashboard.</t>
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>tier-qualification math (T12M ARR threshold + next-tier delta).</t>
+          <t>the SA partner-programme analytics dashboard.</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>FAIL | [2/3] Next-tier T12M ARR threshold target + remaining delta are shown (0ms) -- AssertionError: the next-tier T12M ARR threshold target and remaining delta must be shown in Tier Progress, but only current tier/ARR/deal-count are rendered (panel</t>
+          <t>FAIL | [3/3] The analytics data loads without a server error (44ms) -- AssertionError: the analytics dashboard must load its data, but a query fails with a backend error: 'Server Error limit must not be greater than 100 Server Error Invalid p'. The d</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>FAIL | [2/3] Next-tier T12M ARR threshold target + remaining delta are shown (0ms) -- AssertionError: the next-tier T12M ARR threshold target and remaining delta must be shown in Tier Progress, but only current tier/ARR/deal-count are rendered (panel='Tier &amp; Performance SELECT T12M ARR USD 0 Tier Pr</t>
+          <t>FAIL | [3/3] The analytics data loads without a server error (44ms) -- AssertionError: the analytics dashboard must load its data, but a query fails with a backend error: 'Server Error limit must not be greater than 100 Server Error Invalid p'. The dashboard shell renders but a paginated analytics q</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="O31" s="7" t="n"/>
@@ -2627,74 +2627,146 @@
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
+          <t>BUG-UI-007</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="n">
+        <v>12060405</v>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>PARTNER_UI_DASHBOARD_005</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>tier-qualification math (T12M ARR threshold + next-tier delta).</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>tier-qualification math (T12M ARR threshold + next-tier delta).</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>FAIL | [2/3] Next-tier T12M ARR threshold target + remaining delta are shown (0ms) -- AssertionError: the next-tier T12M ARR threshold target and remaining delta must be shown in Tier Progress, but only current tier/ARR/deal-count are rendered (panel</t>
+        </is>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>FAIL | [2/3] Next-tier T12M ARR threshold target + remaining delta are shown (0ms) -- AssertionError: the next-tier T12M ARR threshold target and remaining delta must be shown in Tier Progress, but only current tier/ARR/deal-count are rendered (panel='Tier &amp; Performance SELECT T12M ARR USD 0 Tier Pr</t>
+        </is>
+      </c>
+      <c r="M32" s="7" t="inlineStr">
+        <is>
+          <t>AI Triage</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="O32" s="7" t="n"/>
+      <c r="P32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
           <t>BUG-UI-008</t>
         </is>
       </c>
-      <c r="B32" s="9" t="n">
+      <c r="B33" s="9" t="n">
         <v>12060515</v>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>PARTNER_UI_SA_PARTNER_MODULE_015</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Partner</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>SA_PARTNER_MODULE</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>suspend (deactivate) an active partner.</t>
         </is>
       </c>
-      <c r="J32" s="7" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>SA can suspend an Active partner from Partner Detail -&gt; Partner actions -&gt; Deactivate: partner transitions to Suspended/Inactive and loses portal access.</t>
         </is>
       </c>
-      <c r="K32" s="7" t="inlineStr">
+      <c r="K33" s="7" t="inlineStr">
         <is>
           <t>Deactivate fails. The "Deactivate Partner" confirm dialog collects NO reason, so the FE calls the deactivate API without one; BE returns 400 Server Error ("reason should not be empty / reason must be a string / reason must be &lt;= 2000 characters"). Partner stays Active. No SA can suspend a partner via the UI.</t>
         </is>
       </c>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>FAIL | [2/2] The partner is suspended and no error is shown (0ms) -- AssertionError: Deactivate failed — the BE rejected the request: 'Failed to deactivate partner Server Error reason must be shorter than or equal to 2000 charactersreason should not be emptyreason must be a string Partner approved Q</t>
         </is>
       </c>
-      <c r="M32" s="7" t="inlineStr">
+      <c r="M33" s="7" t="inlineStr">
         <is>
           <t>AI Triage</t>
         </is>
       </c>
-      <c r="N32" s="7" t="inlineStr">
+      <c r="N33" s="7" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="O32" s="7" t="n"/>
-      <c r="P32" s="7" t="inlineStr">
+      <c r="O33" s="7" t="n"/>
+      <c r="P33" s="7" t="inlineStr">
         <is>
           <t>FE&lt;-&gt;BE contract mismatch. Fix options: (a) add a required Reason textarea to the Deactivate dialog and send it, or (b) make reason optional on the deactivate API. Repro: onboard partner -&gt; Approve -&gt; Partner actions -&gt; Deactivate -&gt; Confirm. Blocks SA_PARTNER_MODULE_016 (reactivate) too. TC marked be_gap.</t>
         </is>

--- a/docs/blazeup/Bug_Tracker.xlsx
+++ b/docs/blazeup/Bug_Tracker.xlsx
@@ -2116,17 +2116,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>DELETE /v1/sa/partners/{id} reports success but only soft-deletes: the record stays in GET /v1/sa/partners with status='suspended', so 'deleted' and 'suspended' are indistinguishable and no client can clean up data it created.</t>
+          <t>Soft delete is INTENTIONAL (confirmed by BE) — but a deleted partner and a suspended one both end up with status='suspended', so no client can tell them apart. The business status 'suspended' has effectively lost its meaning, and QA has no way to remove test data.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>DELETE removes the partner. Or, if soft delete is intentional: deleted records are excluded from GET /v1/sa/partners by default (or expose a deleted/deletedAt flag) so a caller can tell a deleted partner from a suspended one.</t>
+          <t>Keep the soft delete. Add a way to DISTINGUISH the two states — e.g. a read-only deletedAt / isDeleted field, or an optional filter on GET /v1/sa/partners. No behaviour change needed and SA can still see every partner. Separately: a supported way for QA to purge its own test data (maintenance endpoint, or an agreed manual DB cleanup).</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>HTTP 200 {"statusCode":200,"message":"Partner deleted successfully"} — but the record is still returned by GET /v1/sa/partners with status='suspended' and internalNotes='Deleted by SA'. On stgsa 2026-08-06 all 1821 partner records are QA-AUTO test leftovers, the bulk of them already 'deleted' this way.</t>
+          <t>DELETE returns 200 {"message":"Partner deleted successfully"}; the record stays, status flips pending/active -&gt; 'suspended' and internalNotes -&gt; 'Deleted by SA'. That free-text note is the ONLY signal separating a deleted partner from a genuinely suspended one. Measured on stgsa 2026-08-10: 2371 of 2416 partners are 'suspended', and 2369 of those carry 'Deleted by SA' — so only 2 are real suspensions. Volume is also growing: 1808 partners on 2026-08-06 -&gt; 2416 on 2026-08-10 (+608 in 4 days), and nothing can remove them.</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Impact on automation: every created_resources cleanup receives 200 and reports success while removing nothing, so shared staging grows unbounded (~1.8k QA-AUTO partners) and cross-partner conflict tests get noisier over time. No TC asserts that DELETE removes the record (delete_partner is only a cleanup callback) — recommend adding one. Also missing entirely: a DELETE for deals, and a delete/revoke for partner-users (only certifications have one), so data created by PARTNER_UI_MY_PIPELINE_005 and PARTNER_UI_PARTNER_TEAM_001 cannot be cleaned at all. utils/cleanup_staging.py + utils/ui_cleanup.py now verify the effect instead of trusting the 200.</t>
+          <t>BE DESIGN CONFIRMED (Khoa Nguyen, 2026-08-10): partners are never hard-deleted on purpose — SA must see every partner, and the status has to be revertible. So this is NOT a request to hard delete; the remaining ask is only a field that separates 'deleted' from 'suspended'. | Impact on automation: created_resources cleanup receives 200 and reports success while removing nothing — that is how ~2.4k QA-AUTO partners accumulated unnoticed. utils/ui_cleanup.py and utils/cleanup_staging.py now re-read the record after DELETE and report CLEANUP LEAK instead of trusting the status code. | Impact on testing: PARTNER_UI_SA_PARTNER_MODULE_016 (reactivate) needs a genuinely Suspended partner and only 2 candidates exist among 2371 rows. | Also missing, tracked here for now: no DELETE for deals, and no delete/revoke for partner-users (only certifications), so data created by PARTNER_UI_MY_PIPELINE_005 and PARTNER_UI_PARTNER_TEAM_001 cannot be cleaned by any route. | Open question back to Product: should 'application declined' and 'active partner suspended' really share one status too? deactivate serves both.</t>
         </is>
       </c>
     </row>

--- a/docs/blazeup/Bug_Tracker.xlsx
+++ b/docs/blazeup/Bug_Tracker.xlsx
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
@@ -2545,10 +2545,14 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O30" s="7" t="n"/>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>Root cause = contract drift: a plan-slug "pro-v1" (string) is used where the API expects a Mongo _id (24-hex), so deal-list id validation fails. CONSISTENT, not intermittent (updated 2026-08-05): earlier "lucky PASS" runs were a TEST race - the assertion ran before the async deal-list error painted; the test now waits for the fetch to settle and fails deterministically. UI test 12060507 renders fine (shell/filters/headers OK); this step reflects the BE defect. Fix BE so deal-list never returns Invalid id: pro-v1.</t>
+          <t>FIXED — re-verified 2026-08-10: PARTNER_UI_SA_PARTNER_MODULE_007 now PASSES (15.3s, log: 'CHECK deals load -&gt; OK (no server error)'). The deal-list fetch no longer returns "Invalid id: 'pro-v1'". be_gap marker removed from the test and the registry re-synced, so this TC is back inside the merge gate. | Root cause = contract drift: a plan-slug "pro-v1" (string) is used where the API expects a Mongo _id (24-hex), so deal-list id validation fails. CONSISTENT, not intermittent (updated 2026-08-05): earlier "lucky PASS" runs were a TEST race - the assertion ran before the async deal-list error painted; the test now waits for the fetch to settle and fails deterministically. UI test 12060507 renders fine (shell/filters/headers OK); this step reflects the BE defect. Fix BE so deal-list never returns Invalid id: pro-v1.</t>
         </is>
       </c>
     </row>
